--- a/sources/jin_step2.xlsx
+++ b/sources/jin_step2.xlsx
@@ -422,7 +422,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3705,7 +3705,7 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
